--- a/output/pdf_financials_xlsx/HBP.xlsx
+++ b/output/pdf_financials_xlsx/HBP.xlsx
@@ -1269,16 +1269,16 @@
         </is>
       </c>
       <c r="B34" s="3" t="n">
-        <v>0</v>
+        <v>3.252</v>
       </c>
       <c r="C34" s="3" t="n">
-        <v>0</v>
+        <v>0.8080000000000001</v>
       </c>
       <c r="D34" s="3" t="n">
-        <v>0</v>
+        <v>1.081</v>
       </c>
       <c r="E34" s="3" t="n">
-        <v>0</v>
+        <v>0.065</v>
       </c>
     </row>
     <row r="35">
@@ -1307,16 +1307,16 @@
         </is>
       </c>
       <c r="B36" s="3" t="n">
-        <v>0</v>
+        <v>3.252</v>
       </c>
       <c r="C36" s="3" t="n">
-        <v>0</v>
+        <v>0.8080000000000001</v>
       </c>
       <c r="D36" s="3" t="n">
-        <v>0</v>
+        <v>1.081</v>
       </c>
       <c r="E36" s="3" t="n">
-        <v>0</v>
+        <v>0.065</v>
       </c>
     </row>
     <row r="37">
@@ -1535,16 +1535,16 @@
         </is>
       </c>
       <c r="B48" s="3" t="n">
-        <v>3.416</v>
+        <v>0.164</v>
       </c>
       <c r="C48" s="3" t="n">
-        <v>0.8080000000000001</v>
+        <v>0</v>
       </c>
       <c r="D48" s="3" t="n">
-        <v>1.081</v>
+        <v>0</v>
       </c>
       <c r="E48" s="3" t="n">
-        <v>0.065</v>
+        <v>0</v>
       </c>
     </row>
     <row r="49">
@@ -3336,7 +3336,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E3" s="5" t="n">

--- a/output/pdf_financials_xlsx/HBP.xlsx
+++ b/output/pdf_financials_xlsx/HBP.xlsx
@@ -2544,13 +2544,13 @@
         <v>0</v>
       </c>
       <c r="C100" s="3" t="n">
-        <v>0</v>
+        <v>0.013</v>
       </c>
       <c r="D100" s="3" t="n">
-        <v>0</v>
+        <v>0.014</v>
       </c>
       <c r="E100" s="3" t="n">
-        <v>0</v>
+        <v>0.01</v>
       </c>
     </row>
     <row r="101">
@@ -7826,7 +7826,11 @@
           <t>Depreciation of property, plant and equipment</t>
         </is>
       </c>
-      <c r="D129" t="inlineStr"/>
+      <c r="D129" t="inlineStr">
+        <is>
+          <t>DepreciationAmortizationDepletion</t>
+        </is>
+      </c>
       <c r="E129" t="inlineStr">
         <is>
           <t>-</t>
@@ -8810,7 +8814,11 @@
           <t>Depreciation of property, plant and equipment</t>
         </is>
       </c>
-      <c r="D156" t="inlineStr"/>
+      <c r="D156" t="inlineStr">
+        <is>
+          <t>DepreciationAmortizationDepletion</t>
+        </is>
+      </c>
       <c r="E156" t="inlineStr">
         <is>
           <t>-</t>

--- a/output/pdf_financials_xlsx/HBP.xlsx
+++ b/output/pdf_financials_xlsx/HBP.xlsx
@@ -2854,7 +2854,7 @@
         <v>0</v>
       </c>
       <c r="E116" s="3" t="n">
-        <v>0</v>
+        <v>17.963</v>
       </c>
     </row>
     <row r="117">
@@ -8634,7 +8634,11 @@
           <t>Shares issued on acquisition of intangible assets (Notes 5, 6)</t>
         </is>
       </c>
-      <c r="D151" t="inlineStr"/>
+      <c r="D151" t="inlineStr">
+        <is>
+          <t>NetIntangiblesPurchaseAndSale</t>
+        </is>
+      </c>
       <c r="E151" t="inlineStr">
         <is>
           <t>-</t>
@@ -8670,7 +8674,11 @@
           <t>Loan payable assumed on acquisition of intangible assets (Note 5)</t>
         </is>
       </c>
-      <c r="D152" t="inlineStr"/>
+      <c r="D152" t="inlineStr">
+        <is>
+          <t>NetIntangiblesPurchaseAndSale</t>
+        </is>
+      </c>
       <c r="E152" t="inlineStr">
         <is>
           <t>-</t>
